--- a/inputdata/inputdata_pumping.xlsx
+++ b/inputdata/inputdata_pumping.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Itahisa\Desktop\pvlite\inputdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DFFAF56E-B428-4E8D-BFBD-4631FF6DBFC6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CD89AFD-53E3-4E87-8CAE-B68DAC7A0BEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12720" tabRatio="833" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1185,9 +1185,6 @@
     <t>Use_Database_PV</t>
   </si>
   <si>
-    <t>N_modules</t>
-  </si>
-  <si>
     <t>Set to 2 to use PVlite database (1 = Manual Mode, 2 = Use Database)</t>
   </si>
   <si>
@@ -1216,6 +1213,9 @@
   </si>
   <si>
     <t>PV_Degradation_Rate</t>
+  </si>
+  <si>
+    <t>N_Modules</t>
   </si>
 </sst>
 </file>
@@ -1227,7 +1227,7 @@
     <numFmt numFmtId="165" formatCode="0.000"/>
     <numFmt numFmtId="166" formatCode="0.0000"/>
   </numFmts>
-  <fonts count="28">
+  <fonts count="28" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -7225,7 +7225,7 @@
     <tabColor indexed="18"/>
   </sheetPr>
   <dimension ref="A1:F14"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="17.399999999999999"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="2.109375" style="1" customWidth="1"/>
     <col min="2" max="2" width="20.109375" style="2" customWidth="1"/>
@@ -7236,7 +7236,7 @@
     <col min="7" max="16384" width="11.44140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="23.4">
+    <row r="1" spans="1:6" ht="23.4" x14ac:dyDescent="0.55000000000000004">
       <c r="B1" s="79" t="s">
         <v>16</v>
       </c>
@@ -7244,7 +7244,7 @@
       <c r="D1" s="79"/>
       <c r="E1" s="78"/>
     </row>
-    <row r="3" spans="1:6">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A3" s="3"/>
       <c r="B3" s="4" t="s">
         <v>8</v>
@@ -7259,7 +7259,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:6">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A4" s="6">
         <v>1</v>
       </c>
@@ -7276,7 +7276,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:6">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A5" s="6">
         <v>2</v>
       </c>
@@ -7293,7 +7293,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="6" spans="1:6">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A6" s="6">
         <v>3</v>
       </c>
@@ -7310,7 +7310,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="7" spans="1:6">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A7" s="6">
         <v>4</v>
       </c>
@@ -7327,17 +7327,17 @@
         <v>137</v>
       </c>
     </row>
-    <row r="8" spans="1:6">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.4">
       <c r="E8" s="10"/>
     </row>
-    <row r="9" spans="1:6">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.4">
       <c r="E9"/>
       <c r="F9" s="10"/>
     </row>
-    <row r="13" spans="1:6">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.4">
       <c r="F13"/>
     </row>
-    <row r="14" spans="1:6">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.4">
       <c r="E14"/>
     </row>
   </sheetData>
@@ -7376,7 +7376,7 @@
     <tabColor indexed="18"/>
   </sheetPr>
   <dimension ref="A1:L20"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="13.2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="2.5546875" customWidth="1"/>
     <col min="2" max="2" width="19.5546875" customWidth="1"/>
@@ -7385,7 +7385,7 @@
     <col min="5" max="5" width="53" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="23.4">
+    <row r="1" spans="1:12" ht="23.4" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="11"/>
       <c r="B1" s="79" t="s">
         <v>154</v>
@@ -7394,14 +7394,14 @@
       <c r="D1" s="81"/>
       <c r="E1" s="78"/>
     </row>
-    <row r="2" spans="1:12" ht="17.399999999999999">
+    <row r="2" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A2" s="11"/>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
       <c r="D2" s="11"/>
       <c r="E2" s="2"/>
     </row>
-    <row r="3" spans="1:12" ht="17.399999999999999">
+    <row r="3" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A3" s="11"/>
       <c r="B3" s="4" t="s">
         <v>8</v>
@@ -7419,7 +7419,7 @@
       <c r="K3" s="92"/>
       <c r="L3" s="92"/>
     </row>
-    <row r="4" spans="1:12" ht="19.5" customHeight="1">
+    <row r="4" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="24">
         <v>1</v>
       </c>
@@ -7440,7 +7440,7 @@
       <c r="K4" s="92"/>
       <c r="L4" s="92"/>
     </row>
-    <row r="5" spans="1:12" ht="22.5" customHeight="1">
+    <row r="5" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="24">
         <v>2</v>
       </c>
@@ -7460,7 +7460,7 @@
       <c r="K5" s="92"/>
       <c r="L5" s="92"/>
     </row>
-    <row r="6" spans="1:12" ht="21" customHeight="1">
+    <row r="6" spans="1:12" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="24">
         <v>3</v>
       </c>
@@ -7480,7 +7480,7 @@
       <c r="K6" s="92"/>
       <c r="L6" s="92"/>
     </row>
-    <row r="7" spans="1:12" ht="17.399999999999999">
+    <row r="7" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A7" s="24">
         <v>4</v>
       </c>
@@ -7497,7 +7497,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="8" spans="1:12" ht="19.5" customHeight="1">
+    <row r="8" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="24">
         <v>5</v>
       </c>
@@ -7516,7 +7516,7 @@
       </c>
       <c r="F8" s="25"/>
     </row>
-    <row r="9" spans="1:12" ht="17.399999999999999">
+    <row r="9" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A9" s="24">
         <v>6</v>
       </c>
@@ -7529,7 +7529,7 @@
       <c r="F9" s="12"/>
       <c r="G9" s="12"/>
     </row>
-    <row r="10" spans="1:12" ht="19.5" customHeight="1">
+    <row r="10" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="24">
         <v>7</v>
       </c>
@@ -7542,7 +7542,7 @@
       <c r="D10" s="87"/>
       <c r="E10" s="27"/>
     </row>
-    <row r="11" spans="1:12" ht="19.5" customHeight="1">
+    <row r="11" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="24">
         <v>8</v>
       </c>
@@ -7555,7 +7555,7 @@
       <c r="D11" s="87"/>
       <c r="E11" s="27"/>
     </row>
-    <row r="12" spans="1:12" ht="17.399999999999999">
+    <row r="12" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="A12" s="24">
         <v>9</v>
       </c>
@@ -7568,7 +7568,7 @@
       </c>
       <c r="D12" s="11"/>
     </row>
-    <row r="13" spans="1:12" ht="17.399999999999999">
+    <row r="13" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A13" s="24">
         <v>10</v>
       </c>
@@ -7583,7 +7583,7 @@
       <c r="D13" s="12"/>
       <c r="E13" s="25"/>
     </row>
-    <row r="14" spans="1:12" ht="17.399999999999999">
+    <row r="14" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A14" s="24">
         <v>11</v>
       </c>
@@ -7597,7 +7597,7 @@
       </c>
       <c r="D14" s="33"/>
     </row>
-    <row r="15" spans="1:12" ht="17.399999999999999">
+    <row r="15" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A15" s="24">
         <v>12</v>
       </c>
@@ -7612,7 +7612,7 @@
       <c r="D15" s="33"/>
       <c r="E15" s="27"/>
     </row>
-    <row r="16" spans="1:12" ht="17.399999999999999">
+    <row r="16" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A16" s="24">
         <v>13</v>
       </c>
@@ -7627,7 +7627,7 @@
       <c r="D16" s="33"/>
       <c r="E16" s="2"/>
     </row>
-    <row r="17" spans="1:5" ht="17.399999999999999">
+    <row r="17" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A17" s="24">
         <v>14</v>
       </c>
@@ -7642,7 +7642,7 @@
       <c r="D17" s="9"/>
       <c r="E17" s="2"/>
     </row>
-    <row r="18" spans="1:5" ht="17.399999999999999">
+    <row r="18" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A18" s="24">
         <v>15</v>
       </c>
@@ -7656,7 +7656,7 @@
       </c>
       <c r="D18" s="9"/>
     </row>
-    <row r="19" spans="1:5" ht="17.399999999999999">
+    <row r="19" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="A19" s="24">
         <v>16</v>
       </c>
@@ -7669,7 +7669,7 @@
       </c>
       <c r="D19" s="11"/>
     </row>
-    <row r="20" spans="1:5" ht="15">
+    <row r="20" spans="1:5" ht="15" x14ac:dyDescent="0.35">
       <c r="D20" s="11"/>
     </row>
   </sheetData>
@@ -7688,7 +7688,7 @@
     <tabColor indexed="18"/>
   </sheetPr>
   <dimension ref="A1:F95"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="13.2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="2.44140625" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
@@ -7698,7 +7698,7 @@
     <col min="6" max="6" width="12.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="23.4">
+    <row r="1" spans="1:5" ht="23.4" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="11"/>
       <c r="B1" s="79" t="s">
         <v>51</v>
@@ -7707,14 +7707,14 @@
       <c r="D1" s="81"/>
       <c r="E1" s="78"/>
     </row>
-    <row r="2" spans="1:5" ht="17.399999999999999">
+    <row r="2" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A2" s="11"/>
       <c r="B2" s="2"/>
       <c r="C2" s="8"/>
       <c r="D2" s="11"/>
       <c r="E2" s="2"/>
     </row>
-    <row r="3" spans="1:5" ht="17.399999999999999">
+    <row r="3" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A3" s="11"/>
       <c r="B3" s="4" t="s">
         <v>191</v>
@@ -7729,7 +7729,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="17.399999999999999">
+    <row r="4" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A4" s="24">
         <v>1</v>
       </c>
@@ -7746,7 +7746,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="19.8">
+    <row r="5" spans="1:5" ht="19.8" x14ac:dyDescent="0.45">
       <c r="A5" s="24">
         <v>2</v>
       </c>
@@ -7763,7 +7763,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="17.399999999999999">
+    <row r="6" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A6" s="24">
         <v>3</v>
       </c>
@@ -7780,7 +7780,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="19.2">
+    <row r="7" spans="1:5" ht="19.2" x14ac:dyDescent="0.4">
       <c r="A7" s="24">
         <v>4</v>
       </c>
@@ -7798,7 +7798,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="19.2">
+    <row r="8" spans="1:5" ht="19.2" x14ac:dyDescent="0.4">
       <c r="A8" s="24">
         <v>5</v>
       </c>
@@ -7815,7 +7815,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="17.399999999999999">
+    <row r="9" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A9" s="24">
         <v>6</v>
       </c>
@@ -7824,7 +7824,7 @@
       <c r="D9" s="11"/>
       <c r="E9" s="2"/>
     </row>
-    <row r="10" spans="1:5" ht="17.399999999999999">
+    <row r="10" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A10" s="24">
         <v>7</v>
       </c>
@@ -7841,7 +7841,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="18.75" customHeight="1">
+    <row r="11" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A11" s="24">
         <v>8</v>
       </c>
@@ -7858,7 +7858,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="17.399999999999999">
+    <row r="12" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A12" s="24">
         <v>9</v>
       </c>
@@ -7875,7 +7875,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="17.399999999999999">
+    <row r="13" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A13" s="24">
         <v>10</v>
       </c>
@@ -7884,7 +7884,7 @@
       <c r="D13" s="11"/>
       <c r="E13" s="2"/>
     </row>
-    <row r="14" spans="1:5" ht="17.399999999999999">
+    <row r="14" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A14" s="24">
         <v>11</v>
       </c>
@@ -7901,7 +7901,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="15" spans="1:5" ht="19.2">
+    <row r="15" spans="1:5" ht="19.2" x14ac:dyDescent="0.4">
       <c r="A15" s="24">
         <v>12</v>
       </c>
@@ -7918,7 +7918,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="16" spans="1:5" ht="17.399999999999999">
+    <row r="16" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A16" s="24">
         <v>13</v>
       </c>
@@ -7935,7 +7935,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="17" spans="1:6" ht="19.2">
+    <row r="17" spans="1:6" ht="19.2" x14ac:dyDescent="0.4">
       <c r="A17" s="24">
         <v>14</v>
       </c>
@@ -7952,12 +7952,12 @@
         <v>70</v>
       </c>
     </row>
-    <row r="18" spans="1:6">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="24">
         <v>15</v>
       </c>
     </row>
-    <row r="19" spans="1:6" ht="17.399999999999999">
+    <row r="19" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A19" s="24">
         <v>16</v>
       </c>
@@ -7974,7 +7974,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="20" spans="1:6" ht="17.399999999999999">
+    <row r="20" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A20" s="24">
         <v>17</v>
       </c>
@@ -7991,7 +7991,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="21" spans="1:6" ht="17.399999999999999">
+    <row r="21" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A21" s="24">
         <v>18</v>
       </c>
@@ -8009,7 +8009,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="22" spans="1:6" ht="19.2">
+    <row r="22" spans="1:6" ht="19.2" x14ac:dyDescent="0.4">
       <c r="A22" s="24">
         <v>19</v>
       </c>
@@ -8027,7 +8027,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="23" spans="1:6" ht="19.2">
+    <row r="23" spans="1:6" ht="19.2" x14ac:dyDescent="0.4">
       <c r="A23" s="24">
         <v>20</v>
       </c>
@@ -8045,14 +8045,14 @@
         <v>214</v>
       </c>
     </row>
-    <row r="24" spans="1:6" ht="15">
+    <row r="24" spans="1:6" ht="15" x14ac:dyDescent="0.35">
       <c r="A24" s="24">
         <v>21</v>
       </c>
       <c r="D24" s="11"/>
       <c r="F24" s="63"/>
     </row>
-    <row r="25" spans="1:6" ht="17.399999999999999">
+    <row r="25" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A25" s="24">
         <v>22</v>
       </c>
@@ -8062,7 +8062,7 @@
       <c r="C25" s="43"/>
       <c r="D25" s="11"/>
     </row>
-    <row r="26" spans="1:6" ht="19.2">
+    <row r="26" spans="1:6" ht="19.2" x14ac:dyDescent="0.4">
       <c r="A26" s="24">
         <v>23</v>
       </c>
@@ -8074,7 +8074,7 @@
       </c>
       <c r="D26" s="11"/>
     </row>
-    <row r="27" spans="1:6" ht="17.399999999999999">
+    <row r="27" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A27" s="24">
         <v>24</v>
       </c>
@@ -8087,7 +8087,7 @@
       </c>
       <c r="D27" s="11"/>
     </row>
-    <row r="28" spans="1:6" ht="17.399999999999999">
+    <row r="28" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A28" s="24">
         <v>25</v>
       </c>
@@ -8101,7 +8101,7 @@
       </c>
       <c r="D28" s="11"/>
     </row>
-    <row r="29" spans="1:6" ht="17.399999999999999">
+    <row r="29" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A29" s="24">
         <v>26</v>
       </c>
@@ -8115,7 +8115,7 @@
       </c>
       <c r="D29" s="11"/>
     </row>
-    <row r="30" spans="1:6" ht="17.399999999999999">
+    <row r="30" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A30" s="24">
         <v>27</v>
       </c>
@@ -8129,7 +8129,7 @@
       </c>
       <c r="D30" s="11"/>
     </row>
-    <row r="31" spans="1:6" ht="17.399999999999999">
+    <row r="31" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A31" s="24">
         <v>28</v>
       </c>
@@ -8143,7 +8143,7 @@
       </c>
       <c r="D31" s="11"/>
     </row>
-    <row r="32" spans="1:6" ht="17.399999999999999">
+    <row r="32" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A32" s="24">
         <v>29</v>
       </c>
@@ -8157,7 +8157,7 @@
       </c>
       <c r="D32" s="11"/>
     </row>
-    <row r="33" spans="1:5" ht="17.399999999999999">
+    <row r="33" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A33" s="24">
         <v>30</v>
       </c>
@@ -8171,7 +8171,7 @@
       </c>
       <c r="D33" s="11"/>
     </row>
-    <row r="34" spans="1:5" ht="17.399999999999999">
+    <row r="34" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A34" s="24">
         <v>31</v>
       </c>
@@ -8185,7 +8185,7 @@
       </c>
       <c r="D34" s="11"/>
     </row>
-    <row r="35" spans="1:5" ht="17.399999999999999">
+    <row r="35" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A35" s="24">
         <v>32</v>
       </c>
@@ -8199,7 +8199,7 @@
       </c>
       <c r="D35" s="11"/>
     </row>
-    <row r="36" spans="1:5" ht="17.399999999999999">
+    <row r="36" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A36" s="24">
         <v>33</v>
       </c>
@@ -8213,12 +8213,12 @@
       </c>
       <c r="D36" s="11"/>
     </row>
-    <row r="37" spans="1:5">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" s="24">
         <v>34</v>
       </c>
     </row>
-    <row r="38" spans="1:5" ht="17.399999999999999">
+    <row r="38" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A38" s="24">
         <v>35</v>
       </c>
@@ -8229,12 +8229,12 @@
       <c r="D38" s="5"/>
       <c r="E38" s="4"/>
     </row>
-    <row r="39" spans="1:5">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" s="24">
         <v>36</v>
       </c>
     </row>
-    <row r="40" spans="1:5" ht="19.2">
+    <row r="40" spans="1:5" ht="19.2" x14ac:dyDescent="0.4">
       <c r="A40" s="24">
         <v>37</v>
       </c>
@@ -8247,7 +8247,7 @@
       <c r="D40" s="18"/>
       <c r="E40" s="2"/>
     </row>
-    <row r="41" spans="1:5" ht="17.399999999999999">
+    <row r="41" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A41" s="24">
         <v>38</v>
       </c>
@@ -8260,7 +8260,7 @@
       <c r="D41" s="18"/>
       <c r="E41" s="2"/>
     </row>
-    <row r="42" spans="1:5" ht="17.399999999999999">
+    <row r="42" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A42" s="24">
         <v>39</v>
       </c>
@@ -8273,7 +8273,7 @@
       <c r="D42" s="18"/>
       <c r="E42" s="2"/>
     </row>
-    <row r="43" spans="1:5" ht="17.399999999999999">
+    <row r="43" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A43" s="24">
         <v>40</v>
       </c>
@@ -8286,7 +8286,7 @@
       <c r="D43" s="18"/>
       <c r="E43" s="2"/>
     </row>
-    <row r="44" spans="1:5" ht="17.399999999999999">
+    <row r="44" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A44" s="24">
         <v>41</v>
       </c>
@@ -8299,7 +8299,7 @@
       <c r="D44" s="18"/>
       <c r="E44" s="2"/>
     </row>
-    <row r="45" spans="1:5" ht="17.399999999999999">
+    <row r="45" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A45" s="24">
         <v>42</v>
       </c>
@@ -8312,7 +8312,7 @@
       <c r="D45" s="18"/>
       <c r="E45" s="2"/>
     </row>
-    <row r="46" spans="1:5" ht="17.399999999999999">
+    <row r="46" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A46" s="24">
         <v>43</v>
       </c>
@@ -8325,7 +8325,7 @@
       <c r="D46" s="18"/>
       <c r="E46" s="2"/>
     </row>
-    <row r="47" spans="1:5" ht="17.399999999999999">
+    <row r="47" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A47" s="24">
         <v>44</v>
       </c>
@@ -8338,7 +8338,7 @@
       <c r="D47" s="18"/>
       <c r="E47" s="2"/>
     </row>
-    <row r="48" spans="1:5" ht="17.399999999999999">
+    <row r="48" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A48" s="24">
         <v>45</v>
       </c>
@@ -8347,7 +8347,7 @@
       <c r="D48" s="18"/>
       <c r="E48" s="2"/>
     </row>
-    <row r="49" spans="1:5" ht="17.399999999999999">
+    <row r="49" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A49" s="24">
         <v>46</v>
       </c>
@@ -8356,7 +8356,7 @@
       <c r="D49" s="18"/>
       <c r="E49" s="2"/>
     </row>
-    <row r="50" spans="1:5" ht="17.399999999999999">
+    <row r="50" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A50" s="24">
         <v>47</v>
       </c>
@@ -8365,7 +8365,7 @@
       <c r="D50" s="18"/>
       <c r="E50" s="2"/>
     </row>
-    <row r="51" spans="1:5" ht="17.399999999999999">
+    <row r="51" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A51" s="24">
         <v>48</v>
       </c>
@@ -8374,7 +8374,7 @@
       <c r="D51" s="18"/>
       <c r="E51" s="2"/>
     </row>
-    <row r="52" spans="1:5" ht="17.399999999999999">
+    <row r="52" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A52" s="24">
         <v>49</v>
       </c>
@@ -8385,7 +8385,7 @@
       <c r="D52" s="5"/>
       <c r="E52" s="4"/>
     </row>
-    <row r="53" spans="1:5" ht="17.399999999999999">
+    <row r="53" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A53" s="24">
         <v>50</v>
       </c>
@@ -8396,7 +8396,7 @@
       <c r="D53" s="18"/>
       <c r="E53" s="2"/>
     </row>
-    <row r="54" spans="1:5" ht="19.2">
+    <row r="54" spans="1:5" ht="19.2" x14ac:dyDescent="0.4">
       <c r="A54" s="24">
         <v>51</v>
       </c>
@@ -8409,7 +8409,7 @@
       <c r="D54" s="18"/>
       <c r="E54" s="2"/>
     </row>
-    <row r="55" spans="1:5" ht="17.399999999999999">
+    <row r="55" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A55" s="24">
         <v>52</v>
       </c>
@@ -8422,7 +8422,7 @@
       <c r="D55" s="18"/>
       <c r="E55" s="2"/>
     </row>
-    <row r="56" spans="1:5" ht="17.399999999999999">
+    <row r="56" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A56" s="24">
         <v>53</v>
       </c>
@@ -8435,7 +8435,7 @@
       <c r="D56" s="18"/>
       <c r="E56" s="2"/>
     </row>
-    <row r="57" spans="1:5" ht="17.399999999999999">
+    <row r="57" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A57" s="24">
         <v>54</v>
       </c>
@@ -8448,7 +8448,7 @@
       <c r="D57" s="18"/>
       <c r="E57" s="2"/>
     </row>
-    <row r="58" spans="1:5" ht="17.399999999999999">
+    <row r="58" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A58" s="24">
         <v>55</v>
       </c>
@@ -8461,7 +8461,7 @@
       <c r="D58" s="18"/>
       <c r="E58" s="2"/>
     </row>
-    <row r="59" spans="1:5" ht="17.399999999999999">
+    <row r="59" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A59" s="24">
         <v>56</v>
       </c>
@@ -8474,7 +8474,7 @@
       <c r="D59" s="18"/>
       <c r="E59" s="2"/>
     </row>
-    <row r="60" spans="1:5" ht="17.399999999999999">
+    <row r="60" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A60" s="24">
         <v>57</v>
       </c>
@@ -8487,7 +8487,7 @@
       <c r="D60" s="18"/>
       <c r="E60" s="2"/>
     </row>
-    <row r="61" spans="1:5" ht="17.399999999999999">
+    <row r="61" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A61" s="24">
         <v>58</v>
       </c>
@@ -8500,7 +8500,7 @@
       <c r="D61" s="18"/>
       <c r="E61" s="2"/>
     </row>
-    <row r="62" spans="1:5" ht="17.399999999999999">
+    <row r="62" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A62" s="24">
         <v>59</v>
       </c>
@@ -8509,7 +8509,7 @@
       <c r="D62" s="18"/>
       <c r="E62" s="2"/>
     </row>
-    <row r="63" spans="1:5" ht="17.399999999999999">
+    <row r="63" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A63" s="24">
         <v>60</v>
       </c>
@@ -8518,7 +8518,7 @@
       <c r="D63" s="18"/>
       <c r="E63" s="2"/>
     </row>
-    <row r="64" spans="1:5" ht="17.399999999999999">
+    <row r="64" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A64" s="24">
         <v>61</v>
       </c>
@@ -8527,7 +8527,7 @@
       <c r="D64" s="18"/>
       <c r="E64" s="2"/>
     </row>
-    <row r="65" spans="1:6" ht="17.399999999999999">
+    <row r="65" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A65" s="24">
         <v>62</v>
       </c>
@@ -8536,7 +8536,7 @@
       <c r="D65" s="18"/>
       <c r="E65" s="2"/>
     </row>
-    <row r="66" spans="1:6" ht="17.399999999999999">
+    <row r="66" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A66" s="24">
         <v>63</v>
       </c>
@@ -8547,7 +8547,7 @@
       <c r="D66" s="18"/>
       <c r="E66" s="2"/>
     </row>
-    <row r="67" spans="1:6" ht="19.2">
+    <row r="67" spans="1:6" ht="19.2" x14ac:dyDescent="0.4">
       <c r="A67" s="24">
         <v>64</v>
       </c>
@@ -8560,7 +8560,7 @@
       <c r="D67" s="18"/>
       <c r="E67" s="2"/>
     </row>
-    <row r="68" spans="1:6" ht="17.399999999999999">
+    <row r="68" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A68" s="24">
         <v>65</v>
       </c>
@@ -8573,7 +8573,7 @@
       <c r="D68" s="18"/>
       <c r="E68" s="2"/>
     </row>
-    <row r="69" spans="1:6" ht="17.399999999999999">
+    <row r="69" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A69" s="24">
         <v>66</v>
       </c>
@@ -8586,7 +8586,7 @@
       <c r="D69" s="18"/>
       <c r="E69" s="2"/>
     </row>
-    <row r="70" spans="1:6" ht="17.399999999999999">
+    <row r="70" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A70" s="24">
         <v>67</v>
       </c>
@@ -8599,7 +8599,7 @@
       <c r="D70" s="18"/>
       <c r="E70" s="2"/>
     </row>
-    <row r="71" spans="1:6" ht="17.399999999999999">
+    <row r="71" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A71" s="24">
         <v>68</v>
       </c>
@@ -8612,7 +8612,7 @@
       <c r="D71" s="18"/>
       <c r="E71" s="2"/>
     </row>
-    <row r="72" spans="1:6" ht="17.399999999999999">
+    <row r="72" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A72" s="24">
         <v>69</v>
       </c>
@@ -8625,7 +8625,7 @@
       <c r="D72" s="18"/>
       <c r="E72" s="2"/>
     </row>
-    <row r="73" spans="1:6" ht="17.399999999999999">
+    <row r="73" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A73" s="24">
         <v>70</v>
       </c>
@@ -8638,7 +8638,7 @@
       <c r="D73" s="18"/>
       <c r="E73" s="2"/>
     </row>
-    <row r="74" spans="1:6" ht="17.399999999999999">
+    <row r="74" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A74" s="24">
         <v>71</v>
       </c>
@@ -8651,7 +8651,7 @@
       <c r="D74" s="18"/>
       <c r="E74" s="2"/>
     </row>
-    <row r="75" spans="1:6" ht="17.399999999999999">
+    <row r="75" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A75" s="24">
         <v>72</v>
       </c>
@@ -8660,7 +8660,7 @@
       <c r="D75" s="18"/>
       <c r="E75" s="2"/>
     </row>
-    <row r="76" spans="1:6" ht="17.399999999999999">
+    <row r="76" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A76" s="24">
         <v>73</v>
       </c>
@@ -8669,7 +8669,7 @@
       <c r="D76" s="18"/>
       <c r="E76" s="2"/>
     </row>
-    <row r="77" spans="1:6" ht="17.399999999999999">
+    <row r="77" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A77" s="24">
         <v>74</v>
       </c>
@@ -8678,7 +8678,7 @@
       <c r="D77" s="18"/>
       <c r="E77" s="2"/>
     </row>
-    <row r="78" spans="1:6" ht="17.399999999999999">
+    <row r="78" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A78" s="24">
         <v>75</v>
       </c>
@@ -8687,7 +8687,7 @@
       <c r="D78" s="18"/>
       <c r="E78" s="2"/>
     </row>
-    <row r="79" spans="1:6" ht="17.399999999999999">
+    <row r="79" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A79" s="24">
         <v>76</v>
       </c>
@@ -8705,7 +8705,7 @@
       </c>
       <c r="F79" s="25"/>
     </row>
-    <row r="80" spans="1:6" ht="17.399999999999999">
+    <row r="80" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A80" s="24">
         <v>77</v>
       </c>
@@ -8722,7 +8722,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="81" spans="1:5" ht="17.399999999999999">
+    <row r="81" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A81" s="24">
         <v>78</v>
       </c>
@@ -8739,7 +8739,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="82" spans="1:5" ht="37.5" customHeight="1">
+    <row r="82" spans="1:5" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="24">
         <v>79</v>
       </c>
@@ -8756,7 +8756,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="83" spans="1:5" ht="17.399999999999999">
+    <row r="83" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A83" s="24">
         <v>80</v>
       </c>
@@ -8773,7 +8773,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="84" spans="1:5" ht="17.399999999999999">
+    <row r="84" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A84" s="24">
         <v>81</v>
       </c>
@@ -8782,7 +8782,7 @@
       <c r="D84" s="33"/>
       <c r="E84" s="2"/>
     </row>
-    <row r="85" spans="1:5" ht="17.399999999999999">
+    <row r="85" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A85" s="24">
         <v>82</v>
       </c>
@@ -8793,7 +8793,7 @@
       <c r="D85" s="12"/>
       <c r="E85" s="25"/>
     </row>
-    <row r="86" spans="1:5" ht="17.399999999999999">
+    <row r="86" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A86" s="24">
         <v>83</v>
       </c>
@@ -8805,7 +8805,7 @@
       </c>
       <c r="D86" s="33"/>
     </row>
-    <row r="87" spans="1:5" ht="17.399999999999999">
+    <row r="87" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A87" s="24">
         <v>84</v>
       </c>
@@ -8818,7 +8818,7 @@
       <c r="D87" s="33"/>
       <c r="E87" s="27"/>
     </row>
-    <row r="88" spans="1:5" ht="17.399999999999999">
+    <row r="88" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A88" s="24">
         <v>85</v>
       </c>
@@ -8831,7 +8831,7 @@
       <c r="D88" s="33"/>
       <c r="E88" s="2"/>
     </row>
-    <row r="89" spans="1:5" ht="17.399999999999999">
+    <row r="89" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A89" s="24">
         <v>86</v>
       </c>
@@ -8844,7 +8844,7 @@
       <c r="D89" s="9"/>
       <c r="E89" s="2"/>
     </row>
-    <row r="90" spans="1:5" ht="17.399999999999999">
+    <row r="90" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A90" s="24">
         <v>87</v>
       </c>
@@ -8857,7 +8857,7 @@
       <c r="D90" s="9"/>
       <c r="E90" s="2"/>
     </row>
-    <row r="91" spans="1:5" ht="17.399999999999999">
+    <row r="91" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A91" s="24">
         <v>88</v>
       </c>
@@ -8869,7 +8869,7 @@
       </c>
       <c r="D91" s="9"/>
     </row>
-    <row r="92" spans="1:5" ht="17.399999999999999">
+    <row r="92" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A92" s="24">
         <v>89</v>
       </c>
@@ -8882,7 +8882,7 @@
       <c r="D92" s="9"/>
       <c r="E92" s="2"/>
     </row>
-    <row r="93" spans="1:5" ht="17.399999999999999">
+    <row r="93" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A93" s="24">
         <v>90</v>
       </c>
@@ -8895,7 +8895,7 @@
       <c r="D93" s="9"/>
       <c r="E93" s="2"/>
     </row>
-    <row r="94" spans="1:5" ht="17.399999999999999">
+    <row r="94" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A94" s="24">
         <v>91</v>
       </c>
@@ -8904,7 +8904,7 @@
       <c r="D94" s="9"/>
       <c r="E94" s="2"/>
     </row>
-    <row r="95" spans="1:5" ht="15">
+    <row r="95" spans="1:5" ht="15" x14ac:dyDescent="0.35">
       <c r="D95" s="11"/>
     </row>
   </sheetData>
@@ -8932,7 +8932,7 @@
     <tabColor indexed="18"/>
   </sheetPr>
   <dimension ref="A1:E11"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="13.2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="2.6640625" customWidth="1"/>
     <col min="2" max="2" width="37.109375" bestFit="1" customWidth="1"/>
@@ -8941,7 +8941,7 @@
     <col min="5" max="5" width="114.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="23.4">
+    <row r="1" spans="1:5" ht="23.4" x14ac:dyDescent="0.55000000000000004">
       <c r="B1" s="79" t="s">
         <v>34</v>
       </c>
@@ -8949,13 +8949,13 @@
       <c r="D1" s="81"/>
       <c r="E1" s="78"/>
     </row>
-    <row r="2" spans="1:5" ht="17.399999999999999">
+    <row r="2" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
       <c r="D2" s="11"/>
       <c r="E2" s="2"/>
     </row>
-    <row r="3" spans="1:5" ht="17.399999999999999">
+    <row r="3" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="B3" s="4" t="s">
         <v>8</v>
       </c>
@@ -8969,7 +8969,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="17.399999999999999">
+    <row r="4" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="A4" s="24">
         <v>1</v>
       </c>
@@ -8986,7 +8986,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="20.25" customHeight="1">
+    <row r="5" spans="1:5" ht="20.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="24">
         <v>2</v>
       </c>
@@ -9003,7 +9003,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="17.25" customHeight="1">
+    <row r="6" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="24">
         <v>3</v>
       </c>
@@ -9020,7 +9020,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="17.399999999999999">
+    <row r="7" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="A7" s="24">
         <v>4</v>
       </c>
@@ -9037,7 +9037,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="17.399999999999999">
+    <row r="8" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="A8" s="24">
         <v>5</v>
       </c>
@@ -9054,7 +9054,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="17.399999999999999">
+    <row r="9" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.45">
       <c r="A9" s="24">
         <v>6</v>
       </c>
@@ -9071,12 +9071,12 @@
         <v>43</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="17.399999999999999">
+    <row r="10" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.25">
       <c r="A10" s="24">
         <v>7</v>
       </c>
       <c r="B10" s="22" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="C10" s="86">
         <v>25</v>
@@ -9088,12 +9088,12 @@
         <v>283</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="17.399999999999999">
+    <row r="11" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.45">
       <c r="A11" s="24">
         <v>8</v>
       </c>
       <c r="B11" s="22" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C11" s="20"/>
       <c r="D11" s="23" t="s">
@@ -9143,7 +9143,7 @@
     <tabColor rgb="FF000080"/>
   </sheetPr>
   <dimension ref="A1:E12"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="13.2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="2.33203125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="52.5546875" bestFit="1" customWidth="1"/>
@@ -9152,7 +9152,7 @@
     <col min="5" max="5" width="70.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="23.4">
+    <row r="1" spans="1:5" ht="23.4" x14ac:dyDescent="0.55000000000000004">
       <c r="B1" s="79" t="s">
         <v>265</v>
       </c>
@@ -9160,13 +9160,13 @@
       <c r="D1" s="81"/>
       <c r="E1" s="78"/>
     </row>
-    <row r="2" spans="1:5" ht="17.399999999999999">
+    <row r="2" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
       <c r="D2" s="11"/>
       <c r="E2" s="2"/>
     </row>
-    <row r="3" spans="1:5" ht="17.399999999999999">
+    <row r="3" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="B3" s="4" t="s">
         <v>8</v>
       </c>
@@ -9180,7 +9180,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="17.399999999999999">
+    <row r="4" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.45">
       <c r="A4" s="24">
         <v>1</v>
       </c>
@@ -9197,7 +9197,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="17.399999999999999">
+    <row r="5" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.45">
       <c r="A5" s="24">
         <v>2</v>
       </c>
@@ -9214,7 +9214,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="17.399999999999999">
+    <row r="6" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.45">
       <c r="A6" s="24">
         <v>3</v>
       </c>
@@ -9231,7 +9231,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="17.399999999999999">
+    <row r="7" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.45">
       <c r="A7" s="24">
         <v>4</v>
       </c>
@@ -9248,7 +9248,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="17.399999999999999">
+    <row r="8" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.45">
       <c r="A8" s="24">
         <v>5</v>
       </c>
@@ -9265,7 +9265,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="16.8" customHeight="1">
+    <row r="9" spans="1:5" ht="16.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="24">
         <v>6</v>
       </c>
@@ -9282,7 +9282,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="17.399999999999999">
+    <row r="10" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.45">
       <c r="A10" s="24">
         <v>7</v>
       </c>
@@ -9299,7 +9299,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="17.399999999999999">
+    <row r="11" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.45">
       <c r="A11" s="24">
         <v>8</v>
       </c>
@@ -9316,7 +9316,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="17.399999999999999">
+    <row r="12" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.45">
       <c r="A12" s="24">
         <v>9</v>
       </c>
@@ -9344,7 +9344,7 @@
     <tabColor indexed="18"/>
   </sheetPr>
   <dimension ref="A1:L20"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="13.2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="2.44140625" customWidth="1"/>
     <col min="2" max="2" width="12.88671875" customWidth="1"/>
@@ -9357,7 +9357,7 @@
     <col min="12" max="12" width="23.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="23.4">
+    <row r="1" spans="1:12" ht="23.4" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="1"/>
       <c r="B1" s="79" t="s">
         <v>17</v>
@@ -9369,14 +9369,14 @@
       <c r="G1" s="82"/>
       <c r="H1" s="82"/>
     </row>
-    <row r="2" spans="1:12" ht="17.399999999999999">
+    <row r="2" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A2" s="1"/>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
       <c r="E2" s="2"/>
     </row>
-    <row r="3" spans="1:12" ht="17.399999999999999">
+    <row r="3" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A3" s="3"/>
       <c r="B3" s="4" t="s">
         <v>8</v>
@@ -9398,7 +9398,7 @@
       <c r="K3" s="25"/>
       <c r="L3" s="25"/>
     </row>
-    <row r="4" spans="1:12" ht="17.399999999999999">
+    <row r="4" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A4" s="6">
         <v>1</v>
       </c>
@@ -9413,7 +9413,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="5" spans="1:12" ht="17.399999999999999">
+    <row r="5" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A5" s="6">
         <v>2</v>
       </c>
@@ -9428,7 +9428,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="6" spans="1:12" ht="17.399999999999999">
+    <row r="6" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A6" s="6">
         <v>3</v>
       </c>
@@ -9437,12 +9437,12 @@
       <c r="D6" s="9"/>
       <c r="E6" s="2"/>
     </row>
-    <row r="7" spans="1:12" ht="13.8">
+    <row r="7" spans="1:12" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A7" s="6">
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="1:12" ht="19.2">
+    <row r="8" spans="1:12" ht="19.2" x14ac:dyDescent="0.4">
       <c r="A8" s="6">
         <v>5</v>
       </c>
@@ -9462,7 +9462,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="9" spans="1:12" ht="18">
+    <row r="9" spans="1:12" ht="18" x14ac:dyDescent="0.4">
       <c r="A9" s="6">
         <v>6</v>
       </c>
@@ -9485,7 +9485,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="10" spans="1:12" ht="17.399999999999999">
+    <row r="10" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A10" s="6">
         <v>7</v>
       </c>
@@ -9508,7 +9508,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="11" spans="1:12" ht="17.399999999999999">
+    <row r="11" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A11" s="6">
         <v>8</v>
       </c>
@@ -9531,7 +9531,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="12" spans="1:12" ht="17.399999999999999">
+    <row r="12" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A12" s="6">
         <v>9</v>
       </c>
@@ -9548,7 +9548,7 @@
         <v>17.8</v>
       </c>
     </row>
-    <row r="13" spans="1:12" ht="17.399999999999999">
+    <row r="13" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A13" s="6">
         <v>10</v>
       </c>
@@ -9565,7 +9565,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="14" spans="1:12" ht="17.399999999999999">
+    <row r="14" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A14" s="6">
         <v>11</v>
       </c>
@@ -9582,7 +9582,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="15" spans="1:12" ht="17.399999999999999">
+    <row r="15" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A15" s="6">
         <v>12</v>
       </c>
@@ -9599,7 +9599,7 @@
         <v>31.7</v>
       </c>
     </row>
-    <row r="16" spans="1:12" ht="17.399999999999999">
+    <row r="16" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A16" s="6">
         <v>13</v>
       </c>
@@ -9616,7 +9616,7 @@
         <v>31.2</v>
       </c>
     </row>
-    <row r="17" spans="1:5" ht="17.399999999999999">
+    <row r="17" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A17" s="6">
         <v>14</v>
       </c>
@@ -9633,7 +9633,7 @@
         <v>26.1</v>
       </c>
     </row>
-    <row r="18" spans="1:5" ht="17.399999999999999">
+    <row r="18" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A18" s="6">
         <v>15</v>
       </c>
@@ -9650,7 +9650,7 @@
         <v>20.2</v>
       </c>
     </row>
-    <row r="19" spans="1:5" ht="17.399999999999999">
+    <row r="19" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A19" s="6">
         <v>16</v>
       </c>
@@ -9667,7 +9667,7 @@
         <v>13.3</v>
       </c>
     </row>
-    <row r="20" spans="1:5" ht="17.399999999999999">
+    <row r="20" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A20" s="6">
         <v>17</v>
       </c>
@@ -9725,7 +9725,7 @@
     <tabColor indexed="18"/>
   </sheetPr>
   <dimension ref="A1:O22"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="13.2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="2.44140625" customWidth="1"/>
     <col min="2" max="2" width="25.77734375" bestFit="1" customWidth="1"/>
@@ -9737,7 +9737,7 @@
     <col min="15" max="15" width="13.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="23.4">
+    <row r="1" spans="1:15" ht="23.4" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="1"/>
       <c r="B1" s="79" t="s">
         <v>80</v>
@@ -9756,14 +9756,14 @@
       <c r="N1" s="82"/>
       <c r="O1" s="82"/>
     </row>
-    <row r="2" spans="1:15" ht="17.399999999999999">
+    <row r="2" spans="1:15" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A2" s="1"/>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
       <c r="E2" s="2"/>
     </row>
-    <row r="3" spans="1:15" ht="17.399999999999999">
+    <row r="3" spans="1:15" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A3" s="3"/>
       <c r="B3" s="4" t="s">
         <v>8</v>
@@ -9788,7 +9788,7 @@
       <c r="N3" s="82"/>
       <c r="O3" s="82"/>
     </row>
-    <row r="4" spans="1:15" ht="17.399999999999999">
+    <row r="4" spans="1:15" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A4" s="6">
         <v>1</v>
       </c>
@@ -9800,7 +9800,7 @@
       </c>
       <c r="D4" s="110"/>
       <c r="E4" s="109" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="F4" s="109"/>
       <c r="G4" s="109"/>
@@ -9813,7 +9813,7 @@
       <c r="N4" s="109"/>
       <c r="O4" s="109"/>
     </row>
-    <row r="5" spans="1:15" ht="17.399999999999999">
+    <row r="5" spans="1:15" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A5" s="6">
         <v>2</v>
       </c>
@@ -9838,12 +9838,12 @@
       <c r="N5" s="109"/>
       <c r="O5" s="109"/>
     </row>
-    <row r="6" spans="1:15" ht="17.399999999999999">
+    <row r="6" spans="1:15" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A6" s="6">
         <v>3</v>
       </c>
       <c r="B6" s="109" t="s">
-        <v>295</v>
+        <v>305</v>
       </c>
       <c r="C6" s="110">
         <v>4</v>
@@ -9863,7 +9863,7 @@
       <c r="N6" s="109"/>
       <c r="O6" s="109"/>
     </row>
-    <row r="7" spans="1:15" ht="18">
+    <row r="7" spans="1:15" ht="18" x14ac:dyDescent="0.45">
       <c r="A7" s="6">
         <v>4</v>
       </c>
@@ -9881,7 +9881,7 @@
       </c>
       <c r="F7" s="2"/>
     </row>
-    <row r="8" spans="1:15" ht="19.2">
+    <row r="8" spans="1:15" ht="19.2" x14ac:dyDescent="0.4">
       <c r="A8" s="6">
         <v>5</v>
       </c>
@@ -9898,7 +9898,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="9" spans="1:15" ht="15.75" customHeight="1">
+    <row r="9" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="6">
         <v>6</v>
       </c>
@@ -9915,7 +9915,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="10" spans="1:15" ht="15.75" customHeight="1">
+    <row r="10" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="6">
         <v>7</v>
       </c>
@@ -9933,7 +9933,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="11" spans="1:15" ht="17.399999999999999">
+    <row r="11" spans="1:15" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A11" s="6">
         <v>8</v>
       </c>
@@ -9954,7 +9954,7 @@
       <c r="N11" s="4"/>
       <c r="O11" s="4"/>
     </row>
-    <row r="12" spans="1:15" ht="17.399999999999999">
+    <row r="12" spans="1:15" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A12" s="6">
         <v>9</v>
       </c>
@@ -9969,7 +9969,7 @@
       </c>
       <c r="F12" s="2"/>
     </row>
-    <row r="13" spans="1:15" ht="17.399999999999999">
+    <row r="13" spans="1:15" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A13" s="6">
         <v>10</v>
       </c>
@@ -9978,7 +9978,7 @@
       <c r="E13" s="2"/>
       <c r="F13" s="2"/>
     </row>
-    <row r="14" spans="1:15" ht="17.399999999999999">
+    <row r="14" spans="1:15" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A14" s="6">
         <v>11</v>
       </c>
@@ -9990,7 +9990,7 @@
       <c r="E14" s="25"/>
       <c r="F14" s="2"/>
     </row>
-    <row r="15" spans="1:15" ht="18.75" customHeight="1">
+    <row r="15" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A15" s="6">
         <v>12</v>
       </c>
@@ -10014,7 +10014,7 @@
       <c r="K15" s="25"/>
       <c r="L15" s="25"/>
     </row>
-    <row r="16" spans="1:15" ht="17.399999999999999">
+    <row r="16" spans="1:15" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A16" s="6">
         <v>13</v>
       </c>
@@ -10031,7 +10031,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="17" spans="1:12" ht="17.399999999999999">
+    <row r="17" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A17" s="6">
         <v>14</v>
       </c>
@@ -10040,7 +10040,7 @@
       <c r="D17" s="9"/>
       <c r="E17" s="2"/>
     </row>
-    <row r="18" spans="1:12" ht="17.399999999999999">
+    <row r="18" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A18" s="6">
         <v>15</v>
       </c>
@@ -10058,7 +10058,7 @@
       <c r="K18" s="25"/>
       <c r="L18" s="25"/>
     </row>
-    <row r="19" spans="1:12" ht="17.399999999999999">
+    <row r="19" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A19" s="6">
         <v>16</v>
       </c>
@@ -10075,7 +10075,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="20" spans="1:12" ht="17.399999999999999">
+    <row r="20" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A20" s="6">
         <v>17</v>
       </c>
@@ -10084,7 +10084,7 @@
       <c r="D20" s="9"/>
       <c r="E20" s="2"/>
     </row>
-    <row r="21" spans="1:12" ht="17.399999999999999">
+    <row r="21" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A21" s="6">
         <v>18</v>
       </c>
@@ -10095,7 +10095,7 @@
       <c r="D21" s="12"/>
       <c r="E21" s="25"/>
     </row>
-    <row r="22" spans="1:12" ht="17.399999999999999">
+    <row r="22" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A22" s="6">
         <v>19</v>
       </c>
@@ -10156,7 +10156,7 @@
     <tabColor indexed="18"/>
   </sheetPr>
   <dimension ref="A1:E81"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="13.2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="2.6640625" customWidth="1"/>
     <col min="2" max="2" width="20.5546875" customWidth="1"/>
@@ -10165,7 +10165,7 @@
     <col min="5" max="5" width="67.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="23.4">
+    <row r="1" spans="1:5" ht="23.4" x14ac:dyDescent="0.55000000000000004">
       <c r="B1" s="79" t="s">
         <v>35</v>
       </c>
@@ -10173,13 +10173,13 @@
       <c r="D1" s="81"/>
       <c r="E1" s="78"/>
     </row>
-    <row r="2" spans="1:5" ht="18">
+    <row r="2" spans="1:5" ht="18" x14ac:dyDescent="0.45">
       <c r="B2" s="25"/>
       <c r="C2" s="12"/>
       <c r="D2" s="26"/>
       <c r="E2" s="25"/>
     </row>
-    <row r="3" spans="1:5" ht="17.399999999999999">
+    <row r="3" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="B3" s="4" t="s">
         <v>49</v>
       </c>
@@ -10193,7 +10193,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="17.399999999999999">
+    <row r="4" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A4" s="24">
         <v>1</v>
       </c>
@@ -10205,10 +10205,10 @@
       </c>
       <c r="D4" s="110"/>
       <c r="E4" s="109" t="s">
-        <v>296</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" ht="17.399999999999999">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A5" s="24">
         <v>2</v>
       </c>
@@ -10223,7 +10223,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="18.75" customHeight="1">
+    <row r="6" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A6" s="24">
         <v>3</v>
       </c>
@@ -10240,7 +10240,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="18">
+    <row r="7" spans="1:5" ht="18" x14ac:dyDescent="0.45">
       <c r="A7" s="24">
         <v>4</v>
       </c>
@@ -10257,7 +10257,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="18">
+    <row r="8" spans="1:5" ht="18" x14ac:dyDescent="0.45">
       <c r="A8" s="24">
         <v>5</v>
       </c>
@@ -10274,7 +10274,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="18">
+    <row r="9" spans="1:5" ht="18" x14ac:dyDescent="0.45">
       <c r="A9" s="24">
         <v>6</v>
       </c>
@@ -10285,7 +10285,7 @@
       <c r="D9" s="23"/>
       <c r="E9" s="2"/>
     </row>
-    <row r="10" spans="1:5" ht="17.399999999999999">
+    <row r="10" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.45">
       <c r="A10" s="24">
         <v>7</v>
       </c>
@@ -10302,7 +10302,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="17.25" customHeight="1">
+    <row r="11" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A11" s="24">
         <v>8</v>
       </c>
@@ -10319,7 +10319,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="17.25" customHeight="1">
+    <row r="12" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A12" s="24">
         <v>9</v>
       </c>
@@ -10336,7 +10336,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="17.25" customHeight="1">
+    <row r="13" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A13" s="24">
         <v>10</v>
       </c>
@@ -10347,7 +10347,7 @@
       <c r="D13" s="19"/>
       <c r="E13" s="2"/>
     </row>
-    <row r="14" spans="1:5" ht="18">
+    <row r="14" spans="1:5" ht="18" x14ac:dyDescent="0.45">
       <c r="A14" s="24">
         <v>11</v>
       </c>
@@ -10360,7 +10360,7 @@
       <c r="D14" s="19"/>
       <c r="E14" s="2"/>
     </row>
-    <row r="15" spans="1:5" ht="18">
+    <row r="15" spans="1:5" ht="18" x14ac:dyDescent="0.45">
       <c r="A15" s="24">
         <v>12</v>
       </c>
@@ -10373,7 +10373,7 @@
       <c r="D15" s="19"/>
       <c r="E15" s="2"/>
     </row>
-    <row r="16" spans="1:5" ht="18">
+    <row r="16" spans="1:5" ht="18" x14ac:dyDescent="0.45">
       <c r="A16" s="24">
         <v>13</v>
       </c>
@@ -10386,7 +10386,7 @@
       <c r="D16" s="19"/>
       <c r="E16" s="2"/>
     </row>
-    <row r="17" spans="1:5" ht="18">
+    <row r="17" spans="1:5" ht="18" x14ac:dyDescent="0.45">
       <c r="A17" s="24">
         <v>14</v>
       </c>
@@ -10399,7 +10399,7 @@
       <c r="D17" s="19"/>
       <c r="E17" s="2"/>
     </row>
-    <row r="18" spans="1:5" ht="18">
+    <row r="18" spans="1:5" ht="18" x14ac:dyDescent="0.45">
       <c r="A18" s="24">
         <v>15</v>
       </c>
@@ -10412,7 +10412,7 @@
       <c r="D18" s="19"/>
       <c r="E18" s="2"/>
     </row>
-    <row r="19" spans="1:5" ht="18">
+    <row r="19" spans="1:5" ht="18" x14ac:dyDescent="0.45">
       <c r="A19" s="24">
         <v>16</v>
       </c>
@@ -10425,7 +10425,7 @@
       <c r="D19" s="19"/>
       <c r="E19" s="2"/>
     </row>
-    <row r="20" spans="1:5" ht="18">
+    <row r="20" spans="1:5" ht="18" x14ac:dyDescent="0.45">
       <c r="A20" s="24">
         <v>17</v>
       </c>
@@ -10438,127 +10438,127 @@
       <c r="D20" s="19"/>
       <c r="E20" s="2"/>
     </row>
-    <row r="41" spans="4:4" ht="15">
+    <row r="41" spans="4:4" ht="15" x14ac:dyDescent="0.35">
       <c r="D41" s="11"/>
     </row>
-    <row r="42" spans="4:4" ht="15">
+    <row r="42" spans="4:4" ht="15" x14ac:dyDescent="0.35">
       <c r="D42" s="11"/>
     </row>
-    <row r="43" spans="4:4" ht="15">
+    <row r="43" spans="4:4" ht="15" x14ac:dyDescent="0.35">
       <c r="D43" s="11"/>
     </row>
-    <row r="44" spans="4:4" ht="15">
+    <row r="44" spans="4:4" ht="15" x14ac:dyDescent="0.35">
       <c r="D44" s="11"/>
     </row>
-    <row r="45" spans="4:4" ht="15">
+    <row r="45" spans="4:4" ht="15" x14ac:dyDescent="0.35">
       <c r="D45" s="11"/>
     </row>
-    <row r="46" spans="4:4" ht="15">
+    <row r="46" spans="4:4" ht="15" x14ac:dyDescent="0.35">
       <c r="D46" s="11"/>
     </row>
-    <row r="47" spans="4:4" ht="15">
+    <row r="47" spans="4:4" ht="15" x14ac:dyDescent="0.35">
       <c r="D47" s="11"/>
     </row>
-    <row r="48" spans="4:4" ht="15">
+    <row r="48" spans="4:4" ht="15" x14ac:dyDescent="0.35">
       <c r="D48" s="11"/>
     </row>
-    <row r="49" spans="4:4" ht="15">
+    <row r="49" spans="4:4" ht="15" x14ac:dyDescent="0.35">
       <c r="D49" s="11"/>
     </row>
-    <row r="50" spans="4:4" ht="15">
+    <row r="50" spans="4:4" ht="15" x14ac:dyDescent="0.35">
       <c r="D50" s="11"/>
     </row>
-    <row r="51" spans="4:4" ht="15">
+    <row r="51" spans="4:4" ht="15" x14ac:dyDescent="0.35">
       <c r="D51" s="11"/>
     </row>
-    <row r="52" spans="4:4" ht="15">
+    <row r="52" spans="4:4" ht="15" x14ac:dyDescent="0.35">
       <c r="D52" s="11"/>
     </row>
-    <row r="53" spans="4:4" ht="15">
+    <row r="53" spans="4:4" ht="15" x14ac:dyDescent="0.35">
       <c r="D53" s="11"/>
     </row>
-    <row r="54" spans="4:4" ht="15">
+    <row r="54" spans="4:4" ht="15" x14ac:dyDescent="0.35">
       <c r="D54" s="11"/>
     </row>
-    <row r="55" spans="4:4" ht="15">
+    <row r="55" spans="4:4" ht="15" x14ac:dyDescent="0.35">
       <c r="D55" s="11"/>
     </row>
-    <row r="56" spans="4:4" ht="15">
+    <row r="56" spans="4:4" ht="15" x14ac:dyDescent="0.35">
       <c r="D56" s="11"/>
     </row>
-    <row r="57" spans="4:4" ht="15">
+    <row r="57" spans="4:4" ht="15" x14ac:dyDescent="0.35">
       <c r="D57" s="11"/>
     </row>
-    <row r="58" spans="4:4" ht="15">
+    <row r="58" spans="4:4" ht="15" x14ac:dyDescent="0.35">
       <c r="D58" s="11"/>
     </row>
-    <row r="59" spans="4:4" ht="15">
+    <row r="59" spans="4:4" ht="15" x14ac:dyDescent="0.35">
       <c r="D59" s="11"/>
     </row>
-    <row r="60" spans="4:4" ht="15">
+    <row r="60" spans="4:4" ht="15" x14ac:dyDescent="0.35">
       <c r="D60" s="11"/>
     </row>
-    <row r="61" spans="4:4" ht="15">
+    <row r="61" spans="4:4" ht="15" x14ac:dyDescent="0.35">
       <c r="D61" s="11"/>
     </row>
-    <row r="62" spans="4:4" ht="15">
+    <row r="62" spans="4:4" ht="15" x14ac:dyDescent="0.35">
       <c r="D62" s="11"/>
     </row>
-    <row r="63" spans="4:4" ht="15">
+    <row r="63" spans="4:4" ht="15" x14ac:dyDescent="0.35">
       <c r="D63" s="11"/>
     </row>
-    <row r="64" spans="4:4" ht="15">
+    <row r="64" spans="4:4" ht="15" x14ac:dyDescent="0.35">
       <c r="D64" s="11"/>
     </row>
-    <row r="65" spans="4:4" ht="15">
+    <row r="65" spans="4:4" ht="15" x14ac:dyDescent="0.35">
       <c r="D65" s="11"/>
     </row>
-    <row r="66" spans="4:4" ht="15">
+    <row r="66" spans="4:4" ht="15" x14ac:dyDescent="0.35">
       <c r="D66" s="11"/>
     </row>
-    <row r="67" spans="4:4" ht="15">
+    <row r="67" spans="4:4" ht="15" x14ac:dyDescent="0.35">
       <c r="D67" s="11"/>
     </row>
-    <row r="68" spans="4:4" ht="15">
+    <row r="68" spans="4:4" ht="15" x14ac:dyDescent="0.35">
       <c r="D68" s="11"/>
     </row>
-    <row r="69" spans="4:4" ht="15">
+    <row r="69" spans="4:4" ht="15" x14ac:dyDescent="0.35">
       <c r="D69" s="11"/>
     </row>
-    <row r="70" spans="4:4" ht="15">
+    <row r="70" spans="4:4" ht="15" x14ac:dyDescent="0.35">
       <c r="D70" s="11"/>
     </row>
-    <row r="71" spans="4:4" ht="15">
+    <row r="71" spans="4:4" ht="15" x14ac:dyDescent="0.35">
       <c r="D71" s="11"/>
     </row>
-    <row r="72" spans="4:4" ht="15">
+    <row r="72" spans="4:4" ht="15" x14ac:dyDescent="0.35">
       <c r="D72" s="11"/>
     </row>
-    <row r="73" spans="4:4" ht="15">
+    <row r="73" spans="4:4" ht="15" x14ac:dyDescent="0.35">
       <c r="D73" s="11"/>
     </row>
-    <row r="74" spans="4:4" ht="15">
+    <row r="74" spans="4:4" ht="15" x14ac:dyDescent="0.35">
       <c r="D74" s="11"/>
     </row>
-    <row r="75" spans="4:4" ht="15">
+    <row r="75" spans="4:4" ht="15" x14ac:dyDescent="0.35">
       <c r="D75" s="11"/>
     </row>
-    <row r="76" spans="4:4" ht="15">
+    <row r="76" spans="4:4" ht="15" x14ac:dyDescent="0.35">
       <c r="D76" s="11"/>
     </row>
-    <row r="77" spans="4:4" ht="15">
+    <row r="77" spans="4:4" ht="15" x14ac:dyDescent="0.35">
       <c r="D77" s="11"/>
     </row>
-    <row r="78" spans="4:4" ht="15">
+    <row r="78" spans="4:4" ht="15" x14ac:dyDescent="0.35">
       <c r="D78" s="11"/>
     </row>
-    <row r="79" spans="4:4" ht="15">
+    <row r="79" spans="4:4" ht="15" x14ac:dyDescent="0.35">
       <c r="D79" s="11"/>
     </row>
-    <row r="80" spans="4:4" ht="15">
+    <row r="80" spans="4:4" ht="15" x14ac:dyDescent="0.35">
       <c r="D80" s="11"/>
     </row>
-    <row r="81" spans="4:4" ht="15">
+    <row r="81" spans="4:4" ht="15" x14ac:dyDescent="0.35">
       <c r="D81" s="11"/>
     </row>
   </sheetData>
@@ -10591,7 +10591,7 @@
     <tabColor indexed="18"/>
   </sheetPr>
   <dimension ref="A1:E6"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="13.2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="2.33203125" customWidth="1"/>
     <col min="2" max="2" width="12.5546875" customWidth="1"/>
@@ -10600,7 +10600,7 @@
     <col min="5" max="5" width="50.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="23.4">
+    <row r="1" spans="1:5" ht="23.4" x14ac:dyDescent="0.55000000000000004">
       <c r="B1" s="79" t="s">
         <v>33</v>
       </c>
@@ -10608,13 +10608,13 @@
       <c r="D1" s="81"/>
       <c r="E1" s="78"/>
     </row>
-    <row r="2" spans="1:5" ht="17.399999999999999">
+    <row r="2" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
       <c r="D2" s="11"/>
       <c r="E2" s="2"/>
     </row>
-    <row r="3" spans="1:5" ht="17.399999999999999">
+    <row r="3" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="B3" s="4" t="s">
         <v>8</v>
       </c>
@@ -10628,7 +10628,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="17.399999999999999">
+    <row r="4" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.45">
       <c r="A4" s="24">
         <v>1</v>
       </c>
@@ -10645,7 +10645,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="17.399999999999999">
+    <row r="5" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.45">
       <c r="A5" s="24">
         <v>2</v>
       </c>
@@ -10662,7 +10662,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="17.399999999999999">
+    <row r="6" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.45">
       <c r="B6" s="22"/>
       <c r="C6" s="20"/>
       <c r="D6" s="23"/>
@@ -10687,7 +10687,7 @@
     <tabColor indexed="18"/>
   </sheetPr>
   <dimension ref="A1:E6"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="13.2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="2.88671875" customWidth="1"/>
     <col min="2" max="3" width="12.5546875" customWidth="1"/>
@@ -10695,7 +10695,7 @@
     <col min="5" max="5" width="108.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="23.4">
+    <row r="1" spans="1:5" ht="23.4" x14ac:dyDescent="0.55000000000000004">
       <c r="B1" s="79" t="s">
         <v>90</v>
       </c>
@@ -10703,13 +10703,13 @@
       <c r="D1" s="81"/>
       <c r="E1" s="78"/>
     </row>
-    <row r="2" spans="1:5" ht="17.399999999999999">
+    <row r="2" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
       <c r="D2" s="11"/>
       <c r="E2" s="2"/>
     </row>
-    <row r="3" spans="1:5" ht="17.399999999999999">
+    <row r="3" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="B3" s="4" t="s">
         <v>8</v>
       </c>
@@ -10723,7 +10723,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="17.25" customHeight="1">
+    <row r="4" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A4" s="24">
         <v>1</v>
       </c>
@@ -10740,7 +10740,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="18" customHeight="1">
+    <row r="5" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A5" s="24">
         <v>2</v>
       </c>
@@ -10757,7 +10757,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="20.25" customHeight="1">
+    <row r="6" spans="1:5" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A6" s="24">
         <v>3</v>
       </c>
@@ -10785,7 +10785,7 @@
     <tabColor indexed="18"/>
   </sheetPr>
   <dimension ref="A1:E22"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="13.2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="2.33203125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="22.33203125" customWidth="1"/>
@@ -10794,7 +10794,7 @@
     <col min="5" max="5" width="126.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="23.4">
+    <row r="1" spans="1:5" ht="23.4" x14ac:dyDescent="0.55000000000000004">
       <c r="B1" s="79" t="s">
         <v>223</v>
       </c>
@@ -10802,13 +10802,13 @@
       <c r="D1" s="81"/>
       <c r="E1" s="78"/>
     </row>
-    <row r="2" spans="1:5" ht="17.399999999999999">
+    <row r="2" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
       <c r="D2" s="11"/>
       <c r="E2" s="2"/>
     </row>
-    <row r="3" spans="1:5" ht="17.399999999999999">
+    <row r="3" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="B3" s="4" t="s">
         <v>8</v>
       </c>
@@ -10822,27 +10822,27 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="17.399999999999999">
+    <row r="4" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A4" s="24">
         <v>1</v>
       </c>
       <c r="B4" s="109" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C4" s="110">
         <v>1</v>
       </c>
       <c r="D4" s="110"/>
       <c r="E4" s="109" t="s">
-        <v>296</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" ht="17.399999999999999">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A5" s="24">
         <v>2</v>
       </c>
       <c r="B5" s="109" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="C5" s="111" t="s">
         <v>262</v>
@@ -10852,12 +10852,12 @@
         <v>263</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="17.399999999999999">
+    <row r="6" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A6" s="24">
         <v>3</v>
       </c>
       <c r="B6" s="109" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C6" s="110">
         <v>4</v>
@@ -10867,7 +10867,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="17.399999999999999">
+    <row r="7" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.45">
       <c r="A7" s="24">
         <v>4</v>
       </c>
@@ -10884,7 +10884,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="17.399999999999999">
+    <row r="8" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.45">
       <c r="A8" s="24">
         <v>5</v>
       </c>
@@ -10901,7 +10901,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="17.399999999999999">
+    <row r="9" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.45">
       <c r="A9" s="24">
         <v>6</v>
       </c>
@@ -10918,7 +10918,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="17.399999999999999">
+    <row r="10" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.45">
       <c r="A10" s="24">
         <v>7</v>
       </c>
@@ -10935,7 +10935,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="17.399999999999999">
+    <row r="11" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.45">
       <c r="A11" s="24">
         <v>8</v>
       </c>
@@ -10952,7 +10952,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="17.399999999999999">
+    <row r="12" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.45">
       <c r="A12" s="24">
         <v>9</v>
       </c>
@@ -10969,7 +10969,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="17.399999999999999">
+    <row r="13" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.45">
       <c r="A13" s="24">
         <v>10</v>
       </c>
@@ -10986,7 +10986,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="17.399999999999999">
+    <row r="14" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.45">
       <c r="A14" s="24">
         <v>11</v>
       </c>
@@ -11003,7 +11003,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="15" spans="1:5" ht="17.399999999999999">
+    <row r="15" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.45">
       <c r="A15" s="24">
         <v>12</v>
       </c>
@@ -11020,7 +11020,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="16" spans="1:5" ht="17.399999999999999">
+    <row r="16" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.45">
       <c r="A16" s="24">
         <v>13</v>
       </c>
@@ -11037,7 +11037,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="17" spans="1:5" ht="17.399999999999999">
+    <row r="17" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.45">
       <c r="A17" s="24">
         <v>14</v>
       </c>
@@ -11054,12 +11054,12 @@
         <v>247</v>
       </c>
     </row>
-    <row r="18" spans="1:5" ht="17.399999999999999">
+    <row r="18" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.45">
       <c r="A18" s="24">
         <v>15</v>
       </c>
       <c r="B18" s="105" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C18" s="108">
         <v>0</v>
@@ -11071,12 +11071,12 @@
         <v>249</v>
       </c>
     </row>
-    <row r="19" spans="1:5" ht="17.399999999999999">
+    <row r="19" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.45">
       <c r="A19" s="24">
         <v>16</v>
       </c>
       <c r="B19" s="105" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C19" s="108">
         <v>45</v>
@@ -11088,12 +11088,12 @@
         <v>250</v>
       </c>
     </row>
-    <row r="20" spans="1:5" ht="17.399999999999999">
+    <row r="20" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.45">
       <c r="A20" s="24">
         <v>17</v>
       </c>
       <c r="B20" s="105" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="C20" s="108">
         <v>-20</v>
@@ -11105,12 +11105,12 @@
         <v>251</v>
       </c>
     </row>
-    <row r="21" spans="1:5" ht="17.399999999999999">
+    <row r="21" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.45">
       <c r="A21" s="24">
         <v>18</v>
       </c>
       <c r="B21" s="105" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="C21" s="108">
         <v>60</v>
@@ -11122,7 +11122,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="22" spans="1:5" ht="17.399999999999999">
+    <row r="22" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.45">
       <c r="A22" s="24">
         <v>19</v>
       </c>
@@ -11150,7 +11150,7 @@
     <tabColor indexed="18"/>
   </sheetPr>
   <dimension ref="A1:J47"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="13.2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="2.5546875" customWidth="1"/>
     <col min="2" max="2" width="15" customWidth="1"/>
@@ -11163,7 +11163,7 @@
     <col min="9" max="9" width="7.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="23.4">
+    <row r="1" spans="1:10" ht="23.4" x14ac:dyDescent="0.55000000000000004">
       <c r="B1" s="79" t="s">
         <v>91</v>
       </c>
@@ -11171,10 +11171,10 @@
       <c r="D1" s="81"/>
       <c r="E1" s="78"/>
     </row>
-    <row r="2" spans="1:10">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="60"/>
     </row>
-    <row r="3" spans="1:10" ht="17.399999999999999">
+    <row r="3" spans="1:10" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A3" s="24"/>
       <c r="B3" s="4" t="s">
         <v>102</v>
@@ -11184,7 +11184,7 @@
       <c r="E3" s="4"/>
       <c r="J3" s="25"/>
     </row>
-    <row r="4" spans="1:10" ht="17.399999999999999">
+    <row r="4" spans="1:10" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A4" s="24">
         <v>1</v>
       </c>
@@ -11197,7 +11197,7 @@
       <c r="D4" s="8"/>
       <c r="E4" s="2"/>
     </row>
-    <row r="5" spans="1:10" ht="17.399999999999999">
+    <row r="5" spans="1:10" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A5" s="24">
         <v>2</v>
       </c>
@@ -11210,7 +11210,7 @@
       <c r="D5" s="8"/>
       <c r="E5" s="2"/>
     </row>
-    <row r="6" spans="1:10" ht="17.399999999999999">
+    <row r="6" spans="1:10" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A6" s="24">
         <v>3</v>
       </c>
@@ -11223,7 +11223,7 @@
       <c r="D6" s="8"/>
       <c r="E6" s="2"/>
     </row>
-    <row r="7" spans="1:10" ht="17.399999999999999">
+    <row r="7" spans="1:10" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A7" s="24">
         <v>4</v>
       </c>
@@ -11236,7 +11236,7 @@
       <c r="D7" s="8"/>
       <c r="E7" s="2"/>
     </row>
-    <row r="8" spans="1:10" ht="17.399999999999999">
+    <row r="8" spans="1:10" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A8" s="24">
         <v>5</v>
       </c>
@@ -11249,7 +11249,7 @@
       <c r="D8" s="8"/>
       <c r="E8" s="2"/>
     </row>
-    <row r="9" spans="1:10" ht="17.399999999999999">
+    <row r="9" spans="1:10" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A9" s="24">
         <v>6</v>
       </c>
@@ -11262,7 +11262,7 @@
       <c r="D9" s="8"/>
       <c r="E9" s="2"/>
     </row>
-    <row r="10" spans="1:10" ht="17.399999999999999">
+    <row r="10" spans="1:10" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A10" s="24">
         <v>7</v>
       </c>
@@ -11275,7 +11275,7 @@
       <c r="D10" s="8"/>
       <c r="E10" s="2"/>
     </row>
-    <row r="11" spans="1:10" ht="17.399999999999999">
+    <row r="11" spans="1:10" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A11" s="24">
         <v>8</v>
       </c>
@@ -11288,7 +11288,7 @@
       <c r="D11" s="8"/>
       <c r="E11" s="2"/>
     </row>
-    <row r="12" spans="1:10" ht="17.399999999999999">
+    <row r="12" spans="1:10" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A12" s="24">
         <v>9</v>
       </c>
@@ -11301,7 +11301,7 @@
       <c r="D12" s="8"/>
       <c r="E12" s="2"/>
     </row>
-    <row r="13" spans="1:10" ht="17.399999999999999">
+    <row r="13" spans="1:10" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A13" s="24">
         <v>10</v>
       </c>
@@ -11314,7 +11314,7 @@
       <c r="D13" s="8"/>
       <c r="E13" s="2"/>
     </row>
-    <row r="14" spans="1:10" ht="17.399999999999999">
+    <row r="14" spans="1:10" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A14" s="24">
         <v>11</v>
       </c>
@@ -11327,7 +11327,7 @@
       <c r="D14" s="8"/>
       <c r="E14" s="2"/>
     </row>
-    <row r="15" spans="1:10" ht="17.399999999999999">
+    <row r="15" spans="1:10" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A15" s="24">
         <v>12</v>
       </c>
@@ -11340,7 +11340,7 @@
       <c r="D15" s="8"/>
       <c r="E15" s="2"/>
     </row>
-    <row r="16" spans="1:10" ht="17.399999999999999">
+    <row r="16" spans="1:10" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A16" s="24">
         <v>13</v>
       </c>
@@ -11353,7 +11353,7 @@
       <c r="D16" s="8"/>
       <c r="E16" s="2"/>
     </row>
-    <row r="17" spans="1:8" ht="17.399999999999999">
+    <row r="17" spans="1:8" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A17" s="24">
         <v>14</v>
       </c>
@@ -11369,12 +11369,12 @@
         <v>109</v>
       </c>
     </row>
-    <row r="18" spans="1:8">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" s="24">
         <v>15</v>
       </c>
     </row>
-    <row r="19" spans="1:8" ht="15.75" customHeight="1">
+    <row r="19" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" s="24">
         <v>16</v>
       </c>
@@ -11383,7 +11383,7 @@
       <c r="D19" s="9"/>
       <c r="E19" s="2"/>
     </row>
-    <row r="20" spans="1:8" ht="17.399999999999999">
+    <row r="20" spans="1:8" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A20" s="24">
         <v>17</v>
       </c>
@@ -11394,7 +11394,7 @@
       <c r="D20" s="5"/>
       <c r="E20" s="4"/>
     </row>
-    <row r="21" spans="1:8" ht="17.399999999999999">
+    <row r="21" spans="1:8" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A21" s="24">
         <v>18</v>
       </c>
@@ -11403,7 +11403,7 @@
       <c r="D21" s="12"/>
       <c r="E21" s="25"/>
     </row>
-    <row r="22" spans="1:8" ht="17.399999999999999">
+    <row r="22" spans="1:8" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A22" s="24">
         <v>19</v>
       </c>
@@ -11418,7 +11418,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="23" spans="1:8" ht="18">
+    <row r="23" spans="1:8" ht="18" x14ac:dyDescent="0.45">
       <c r="A23" s="24">
         <v>20</v>
       </c>
@@ -11433,7 +11433,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="24" spans="1:8" ht="18">
+    <row r="24" spans="1:8" ht="18" x14ac:dyDescent="0.45">
       <c r="A24" s="24">
         <v>21</v>
       </c>
@@ -11445,7 +11445,7 @@
       </c>
       <c r="D24" s="19"/>
     </row>
-    <row r="25" spans="1:8" ht="19.8">
+    <row r="25" spans="1:8" ht="19.8" x14ac:dyDescent="0.45">
       <c r="A25" s="24">
         <v>22</v>
       </c>
@@ -11467,7 +11467,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="26" spans="1:8" ht="17.399999999999999">
+    <row r="26" spans="1:8" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A26" s="24">
         <v>23</v>
       </c>
@@ -11479,7 +11479,7 @@
       </c>
       <c r="D26" s="11"/>
     </row>
-    <row r="27" spans="1:8" ht="17.399999999999999">
+    <row r="27" spans="1:8" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A27" s="24">
         <v>24</v>
       </c>
@@ -11491,7 +11491,7 @@
       </c>
       <c r="D27" s="11"/>
     </row>
-    <row r="28" spans="1:8" ht="17.399999999999999">
+    <row r="28" spans="1:8" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A28" s="24">
         <v>25</v>
       </c>
@@ -11503,7 +11503,7 @@
       </c>
       <c r="D28" s="11"/>
     </row>
-    <row r="29" spans="1:8" ht="17.399999999999999">
+    <row r="29" spans="1:8" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A29" s="24">
         <v>26</v>
       </c>
@@ -11515,7 +11515,7 @@
       </c>
       <c r="D29" s="11"/>
     </row>
-    <row r="30" spans="1:8" ht="17.399999999999999">
+    <row r="30" spans="1:8" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A30" s="24">
         <v>27</v>
       </c>
@@ -11527,7 +11527,7 @@
       </c>
       <c r="D30" s="11"/>
     </row>
-    <row r="31" spans="1:8" ht="17.399999999999999">
+    <row r="31" spans="1:8" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A31" s="24">
         <v>28</v>
       </c>
@@ -11539,7 +11539,7 @@
       </c>
       <c r="D31" s="11"/>
     </row>
-    <row r="32" spans="1:8" ht="17.399999999999999">
+    <row r="32" spans="1:8" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A32" s="24">
         <v>29</v>
       </c>
@@ -11551,7 +11551,7 @@
       </c>
       <c r="D32" s="11"/>
     </row>
-    <row r="33" spans="1:4" ht="17.399999999999999">
+    <row r="33" spans="1:4" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A33" s="24">
         <v>30</v>
       </c>
@@ -11563,7 +11563,7 @@
       </c>
       <c r="D33" s="11"/>
     </row>
-    <row r="34" spans="1:4" ht="17.399999999999999">
+    <row r="34" spans="1:4" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A34" s="24">
         <v>31</v>
       </c>
@@ -11575,7 +11575,7 @@
       </c>
       <c r="D34" s="11"/>
     </row>
-    <row r="35" spans="1:4" ht="17.399999999999999">
+    <row r="35" spans="1:4" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A35" s="24">
         <v>32</v>
       </c>
@@ -11587,7 +11587,7 @@
       </c>
       <c r="D35" s="11"/>
     </row>
-    <row r="36" spans="1:4" ht="17.399999999999999">
+    <row r="36" spans="1:4" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A36" s="24">
         <v>33</v>
       </c>
@@ -11599,7 +11599,7 @@
       </c>
       <c r="D36" s="11"/>
     </row>
-    <row r="37" spans="1:4" ht="17.399999999999999">
+    <row r="37" spans="1:4" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A37" s="24">
         <v>34</v>
       </c>
@@ -11611,7 +11611,7 @@
       </c>
       <c r="D37" s="11"/>
     </row>
-    <row r="38" spans="1:4" ht="17.399999999999999">
+    <row r="38" spans="1:4" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A38" s="24">
         <v>35</v>
       </c>
@@ -11623,7 +11623,7 @@
       </c>
       <c r="D38" s="11"/>
     </row>
-    <row r="39" spans="1:4" ht="17.399999999999999">
+    <row r="39" spans="1:4" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A39" s="24">
         <v>36</v>
       </c>
@@ -11635,7 +11635,7 @@
       </c>
       <c r="D39" s="11"/>
     </row>
-    <row r="40" spans="1:4" ht="17.399999999999999">
+    <row r="40" spans="1:4" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A40" s="24">
         <v>37</v>
       </c>
@@ -11647,7 +11647,7 @@
       </c>
       <c r="D40" s="11"/>
     </row>
-    <row r="41" spans="1:4" ht="17.399999999999999">
+    <row r="41" spans="1:4" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A41" s="24">
         <v>38</v>
       </c>
@@ -11659,7 +11659,7 @@
       </c>
       <c r="D41" s="11"/>
     </row>
-    <row r="42" spans="1:4" ht="17.399999999999999">
+    <row r="42" spans="1:4" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A42" s="24">
         <v>39</v>
       </c>
@@ -11671,7 +11671,7 @@
       </c>
       <c r="D42" s="11"/>
     </row>
-    <row r="43" spans="1:4" ht="17.399999999999999">
+    <row r="43" spans="1:4" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A43" s="24">
         <v>40</v>
       </c>
@@ -11683,7 +11683,7 @@
       </c>
       <c r="D43" s="11"/>
     </row>
-    <row r="44" spans="1:4" ht="17.399999999999999">
+    <row r="44" spans="1:4" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A44" s="24">
         <v>41</v>
       </c>
@@ -11695,7 +11695,7 @@
       </c>
       <c r="D44" s="11"/>
     </row>
-    <row r="45" spans="1:4" ht="17.399999999999999">
+    <row r="45" spans="1:4" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A45" s="24">
         <v>42</v>
       </c>
@@ -11707,7 +11707,7 @@
       </c>
       <c r="D45" s="11"/>
     </row>
-    <row r="46" spans="1:4" ht="17.399999999999999">
+    <row r="46" spans="1:4" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A46" s="24">
         <v>43</v>
       </c>
@@ -11719,7 +11719,7 @@
       </c>
       <c r="D46" s="11"/>
     </row>
-    <row r="47" spans="1:4" ht="17.399999999999999">
+    <row r="47" spans="1:4" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="B47" s="2" t="s">
         <v>100</v>
       </c>
@@ -11746,7 +11746,7 @@
     <tabColor indexed="18"/>
   </sheetPr>
   <dimension ref="A1:I26"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="13.2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="2.44140625" customWidth="1"/>
     <col min="2" max="2" width="21" customWidth="1"/>
@@ -11756,7 +11756,7 @@
     <col min="6" max="6" width="11.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="23.4">
+    <row r="1" spans="1:9" ht="23.4" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="11"/>
       <c r="B1" s="79" t="s">
         <v>108</v>
@@ -11765,14 +11765,14 @@
       <c r="D1" s="81"/>
       <c r="E1" s="78"/>
     </row>
-    <row r="2" spans="1:9" ht="17.399999999999999">
+    <row r="2" spans="1:9" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A2" s="11"/>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
       <c r="D2" s="11"/>
       <c r="E2" s="2"/>
     </row>
-    <row r="3" spans="1:9" ht="17.399999999999999">
+    <row r="3" spans="1:9" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A3" s="11"/>
       <c r="B3" s="4" t="s">
         <v>8</v>
@@ -11787,7 +11787,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="19.5" customHeight="1">
+    <row r="4" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="24">
         <v>1</v>
       </c>
@@ -11805,7 +11805,7 @@
       </c>
       <c r="F4" s="63"/>
     </row>
-    <row r="5" spans="1:9" ht="17.399999999999999">
+    <row r="5" spans="1:9" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A5" s="24">
         <v>2</v>
       </c>
@@ -11822,7 +11822,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="6" spans="1:9" ht="20.25" customHeight="1">
+    <row r="6" spans="1:9" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="24">
         <v>3</v>
       </c>
@@ -11839,13 +11839,13 @@
         <v>128</v>
       </c>
     </row>
-    <row r="7" spans="1:9" ht="15">
+    <row r="7" spans="1:9" ht="15" x14ac:dyDescent="0.35">
       <c r="A7" s="24">
         <v>4</v>
       </c>
       <c r="D7" s="11"/>
     </row>
-    <row r="8" spans="1:9" ht="17.399999999999999">
+    <row r="8" spans="1:9" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A8" s="24">
         <v>5</v>
       </c>
@@ -11862,7 +11862,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="9" spans="1:9" ht="19.5" customHeight="1">
+    <row r="9" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="24">
         <v>6</v>
       </c>
@@ -11879,7 +11879,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="10" spans="1:9" ht="21" customHeight="1">
+    <row r="10" spans="1:9" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="24">
         <v>7</v>
       </c>
@@ -11897,7 +11897,7 @@
       </c>
       <c r="I10" s="27"/>
     </row>
-    <row r="11" spans="1:9" ht="19.5" customHeight="1">
+    <row r="11" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="24">
         <v>8</v>
       </c>
@@ -11914,7 +11914,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="12" spans="1:9" ht="19.5" customHeight="1">
+    <row r="12" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="24">
         <v>9</v>
       </c>
@@ -11931,7 +11931,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="13" spans="1:9" ht="19.5" customHeight="1">
+    <row r="13" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="24">
         <v>10</v>
       </c>
@@ -11940,7 +11940,7 @@
       <c r="D13" s="87"/>
       <c r="E13" s="27"/>
     </row>
-    <row r="14" spans="1:9" ht="19.5" customHeight="1">
+    <row r="14" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A14" s="24">
         <v>11</v>
       </c>
@@ -11951,7 +11951,7 @@
       <c r="D14" s="87"/>
       <c r="E14" s="27"/>
     </row>
-    <row r="15" spans="1:9" ht="19.5" customHeight="1">
+    <row r="15" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A15" s="24">
         <v>12</v>
       </c>
@@ -11964,7 +11964,7 @@
       <c r="D15" s="87"/>
       <c r="E15" s="27"/>
     </row>
-    <row r="16" spans="1:9" ht="19.5" customHeight="1">
+    <row r="16" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="24">
         <v>13</v>
       </c>
@@ -11978,7 +11978,7 @@
       <c r="D16" s="87"/>
       <c r="E16" s="27"/>
     </row>
-    <row r="17" spans="1:5" ht="17.399999999999999">
+    <row r="17" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="A17" s="24">
         <v>14</v>
       </c>
@@ -11992,7 +11992,7 @@
       </c>
       <c r="D17" s="11"/>
     </row>
-    <row r="18" spans="1:5" ht="17.399999999999999">
+    <row r="18" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A18" s="24">
         <v>15</v>
       </c>
@@ -12007,7 +12007,7 @@
       <c r="D18" s="12"/>
       <c r="E18" s="25"/>
     </row>
-    <row r="19" spans="1:5" ht="17.399999999999999">
+    <row r="19" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A19" s="24">
         <v>16</v>
       </c>
@@ -12021,7 +12021,7 @@
       </c>
       <c r="D19" s="33"/>
     </row>
-    <row r="20" spans="1:5" ht="17.399999999999999">
+    <row r="20" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A20" s="24">
         <v>17</v>
       </c>
@@ -12036,25 +12036,25 @@
       <c r="D20" s="33"/>
       <c r="E20" s="27"/>
     </row>
-    <row r="21" spans="1:5" ht="17.399999999999999">
+    <row r="21" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="D21" s="33"/>
       <c r="E21" s="2"/>
     </row>
-    <row r="22" spans="1:5" ht="17.399999999999999">
+    <row r="22" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="D22" s="9"/>
       <c r="E22" s="2"/>
     </row>
-    <row r="23" spans="1:5" ht="17.399999999999999">
+    <row r="23" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="D23" s="9"/>
       <c r="E23" s="2"/>
     </row>
-    <row r="24" spans="1:5" ht="17.399999999999999">
+    <row r="24" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="D24" s="9"/>
     </row>
-    <row r="25" spans="1:5" ht="15">
+    <row r="25" spans="1:5" ht="15" x14ac:dyDescent="0.35">
       <c r="D25" s="11"/>
     </row>
-    <row r="26" spans="1:5" ht="15">
+    <row r="26" spans="1:5" ht="15" x14ac:dyDescent="0.35">
       <c r="D26" s="11"/>
     </row>
   </sheetData>

--- a/inputdata/inputdata_pumping.xlsx
+++ b/inputdata/inputdata_pumping.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Itahisa\Desktop\pvlite\inputdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CD89AFD-53E3-4E87-8CAE-B68DAC7A0BEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26D0994B-930E-4109-99E2-4318BB5E7EBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12720" tabRatio="833" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12720" tabRatio="833" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Site" sheetId="6" r:id="rId1"/>
@@ -9095,7 +9095,9 @@
       <c r="B11" s="22" t="s">
         <v>304</v>
       </c>
-      <c r="C11" s="20"/>
+      <c r="C11" s="20">
+        <v>0</v>
+      </c>
       <c r="D11" s="23" t="s">
         <v>7</v>
       </c>

--- a/inputdata/inputdata_pumping.xlsx
+++ b/inputdata/inputdata_pumping.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Itahisa\Desktop\pvlite\inputdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26D0994B-930E-4109-99E2-4318BB5E7EBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8393286-87EE-4460-AE31-249CB0266CF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12720" tabRatio="833" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12720" tabRatio="833" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Site" sheetId="6" r:id="rId1"/>
@@ -9798,7 +9798,7 @@
         <v>294</v>
       </c>
       <c r="C4" s="110">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D4" s="110"/>
       <c r="E4" s="109" t="s">
@@ -10203,7 +10203,7 @@
         <v>292</v>
       </c>
       <c r="C4" s="110">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D4" s="110"/>
       <c r="E4" s="109" t="s">
@@ -10832,7 +10832,7 @@
         <v>296</v>
       </c>
       <c r="C4" s="110">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D4" s="110"/>
       <c r="E4" s="109" t="s">
